--- a/Study_Plan_and_Interviews_Preparation/Mediatek Interview Process/Mediatek_Income_Estimation_Model_Aug2026_Dec2028.xlsx
+++ b/Study_Plan_and_Interviews_Preparation/Mediatek Interview Process/Mediatek_Income_Estimation_Model_Aug2026_Dec2028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal_Stuff\Study_Plan_and_Interviews_Preparation\Mediatek Interview Process\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB4807A-EAF8-4E69-973A-F0098076D603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A121D46B-171C-4C03-8C83-E5F0EFB573E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -119,9 +119,6 @@
     <t>Short-Term Bonus</t>
   </si>
   <si>
-    <t>LPTA Paid</t>
-  </si>
-  <si>
     <t>Total Monthly Income</t>
   </si>
   <si>
@@ -144,6 +141,9 @@
   </si>
   <si>
     <t>Total Income in 2028</t>
+  </si>
+  <si>
+    <t>LPTA Bonus</t>
   </si>
 </sst>
 </file>
@@ -213,7 +213,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -236,11 +236,70 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -260,9 +319,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -274,6 +330,25 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -462,76 +537,76 @@
                   <c:v>2760</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2840.5</c:v>
+                  <c:v>2760</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4324</c:v>
+                  <c:v>2760</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2840.5</c:v>
+                  <c:v>2760</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2840.5</c:v>
+                  <c:v>2760</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2840.5</c:v>
+                  <c:v>2760</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2840.5</c:v>
+                  <c:v>2760</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2840.5</c:v>
+                  <c:v>2760</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>4551.01</c:v>
+                  <c:v>2760</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2840.5</c:v>
+                  <c:v>2760</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2840.5</c:v>
+                  <c:v>2760</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2840.5</c:v>
+                  <c:v>2760</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2840.5</c:v>
+                  <c:v>2760</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3039.3350000000005</c:v>
+                  <c:v>2760</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>6028.0700000000015</c:v>
+                  <c:v>2760</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3039.3350000000005</c:v>
+                  <c:v>2760</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3039.3350000000005</c:v>
+                  <c:v>2760</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>3039.3350000000005</c:v>
+                  <c:v>2760</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>3039.3350000000005</c:v>
+                  <c:v>2760</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>3039.3350000000005</c:v>
+                  <c:v>2760</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>6111.5807000000004</c:v>
+                  <c:v>2760</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>3039.3350000000005</c:v>
+                  <c:v>2760</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>3039.3350000000005</c:v>
+                  <c:v>2760</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>3039.3350000000005</c:v>
+                  <c:v>2760</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>3039.3350000000005</c:v>
+                  <c:v>2760</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -986,11 +1061,11 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
@@ -1017,11 +1092,11 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
@@ -1036,7 +1111,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="5">
-        <v>7.0000000000000007E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -1053,22 +1128,22 @@
         <v>9</v>
       </c>
       <c r="B11" s="5">
-        <v>7.0000000000000007E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="5">
-        <v>7.0000000000000007E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -1088,54 +1163,54 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B17" s="5">
-        <v>0.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
     </row>
     <row r="21" spans="1:3" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
     </row>
     <row r="22" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
     </row>
     <row r="23" spans="1:3" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
     </row>
     <row r="24" spans="1:3" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -1155,7 +1230,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
@@ -1165,11 +1240,13 @@
     <col min="6" max="6" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.44140625" customWidth="1"/>
-    <col min="9" max="9" width="11.6640625" customWidth="1"/>
-    <col min="10" max="10" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>21</v>
       </c>
@@ -1180,25 +1257,25 @@
         <v>22</v>
       </c>
       <c r="D1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="8">
         <v>46235</v>
       </c>
@@ -1211,28 +1288,25 @@
         <v>0</v>
       </c>
       <c r="D2" s="9">
-        <f t="shared" ref="D2:D30" si="2">SUMIFS($J$2:$J$7,$I$2:$I$7,"&gt;="&amp;$A2,$I$2:$I$7,"&lt;"&amp;EDATE($A2,1))</f>
+        <f>SUMIFS($L$2:$L$7,$K$2:$K$7,"&gt;="&amp;$A2,$K$2:$K$7,"&lt;"&amp;EDATE($A2,1))</f>
         <v>0</v>
       </c>
       <c r="E2" s="9">
-        <f t="shared" ref="E2:E30" si="3">SUM(B2:D2)</f>
-        <v>2760</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="H2">
+        <f t="shared" ref="E2:E30" si="2">SUM(B2:D2)</f>
+        <v>2760</v>
+      </c>
+      <c r="J2">
         <v>2026</v>
       </c>
-      <c r="I2" s="10">
+      <c r="K2" s="10">
         <v>46419</v>
       </c>
-      <c r="J2" s="11">
+      <c r="L2" s="11">
         <f>(IF(2026=2026,Base_Annual_Salary_2026,IF(2026=2027,Base_Annual_Salary_2026*(1+Appraisal_Raise_Pct_Jan2027*Appraisal_Proration_Jan2027),(Base_Annual_Salary_2026*(1+Appraisal_Raise_Pct_Jan2027*Appraisal_Proration_Jan2027))*(1+Appraisal_Raise_Pct_Jan2028))))*LPTA_Annual_Grant_Pct*Appraisal_Proration_Jan2027/4</f>
-        <v>517.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <f>EDATE($A$2,1)</f>
         <v>46266</v>
@@ -1246,29 +1320,25 @@
         <v>0</v>
       </c>
       <c r="D3" s="9">
-        <f t="shared" si="2"/>
+        <f>SUMIFS($L$2:$L$7,$K$2:$K$7,"&gt;="&amp;$A3,$K$2:$K$7,"&lt;"&amp;EDATE($A3,1))</f>
         <v>0</v>
       </c>
       <c r="E3" s="9">
-        <f t="shared" si="3"/>
-        <v>2760</v>
-      </c>
-      <c r="F3" s="13">
-        <f>SUM(E2:E6)</f>
-        <v>13800</v>
-      </c>
-      <c r="H3">
+        <f t="shared" si="2"/>
+        <v>2760</v>
+      </c>
+      <c r="J3">
         <v>2026</v>
       </c>
-      <c r="I3" s="10">
+      <c r="K3" s="10">
         <v>46600</v>
       </c>
-      <c r="J3" s="11">
+      <c r="L3" s="11">
         <f>(IF(2026=2026,Base_Annual_Salary_2026,IF(2026=2027,Base_Annual_Salary_2026*(1+Appraisal_Raise_Pct_Jan2027*Appraisal_Proration_Jan2027),(Base_Annual_Salary_2026*(1+Appraisal_Raise_Pct_Jan2027*Appraisal_Proration_Jan2027))*(1+Appraisal_Raise_Pct_Jan2028))))*LPTA_Annual_Grant_Pct*Appraisal_Proration_Jan2027/4</f>
-        <v>517.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <f>EDATE($A$2,2)</f>
         <v>46296</v>
@@ -1282,26 +1352,26 @@
         <v>0</v>
       </c>
       <c r="D4" s="9">
-        <f t="shared" si="2"/>
+        <f>SUMIFS($L$2:$L$7,$K$2:$K$7,"&gt;="&amp;$A4,$K$2:$K$7,"&lt;"&amp;EDATE($A4,1))</f>
         <v>0</v>
       </c>
       <c r="E4" s="9">
-        <f t="shared" si="3"/>
-        <v>2760</v>
-      </c>
-      <c r="F4" s="14"/>
-      <c r="H4">
+        <f t="shared" si="2"/>
+        <v>2760</v>
+      </c>
+      <c r="F4" s="13"/>
+      <c r="J4">
         <v>2026</v>
       </c>
-      <c r="I4" s="10">
+      <c r="K4" s="10">
         <v>46784</v>
       </c>
-      <c r="J4" s="11">
+      <c r="L4" s="11">
         <f>(IF(2026=2026,Base_Annual_Salary_2026,IF(2026=2027,Base_Annual_Salary_2026*(1+Appraisal_Raise_Pct_Jan2027*Appraisal_Proration_Jan2027),(Base_Annual_Salary_2026*(1+Appraisal_Raise_Pct_Jan2027*Appraisal_Proration_Jan2027))*(1+Appraisal_Raise_Pct_Jan2028))))*LPTA_Annual_Grant_Pct*Appraisal_Proration_Jan2027/4</f>
-        <v>517.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <f>EDATE($A$2,3)</f>
         <v>46327</v>
@@ -1315,619 +1385,630 @@
         <v>0</v>
       </c>
       <c r="D5" s="9">
-        <f t="shared" si="2"/>
+        <f>SUMIFS($L$2:$L$7,$K$2:$K$7,"&gt;="&amp;$A5,$K$2:$K$7,"&lt;"&amp;EDATE($A5,1))</f>
         <v>0</v>
       </c>
       <c r="E5" s="9">
-        <f t="shared" si="3"/>
-        <v>2760</v>
-      </c>
-      <c r="F5" s="14"/>
-      <c r="H5">
+        <f t="shared" si="2"/>
+        <v>2760</v>
+      </c>
+      <c r="F5" s="13"/>
+      <c r="G5" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5">
         <v>2026</v>
       </c>
-      <c r="I5" s="10">
+      <c r="K5" s="10">
         <v>46966</v>
       </c>
-      <c r="J5" s="11">
+      <c r="L5" s="11">
         <f>(IF(2026=2026,Base_Annual_Salary_2026,IF(2026=2027,Base_Annual_Salary_2026*(1+Appraisal_Raise_Pct_Jan2027*Appraisal_Proration_Jan2027),(Base_Annual_Salary_2026*(1+Appraisal_Raise_Pct_Jan2027*Appraisal_Proration_Jan2027))*(1+Appraisal_Raise_Pct_Jan2028))))*LPTA_Annual_Grant_Pct*Appraisal_Proration_Jan2027/4</f>
-        <v>517.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="20">
         <f>EDATE($A$2,4)</f>
         <v>46357</v>
       </c>
-      <c r="B6" s="9">
-        <f t="shared" si="0"/>
-        <v>2760</v>
-      </c>
-      <c r="C6" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D6" s="9">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E6" s="9">
-        <f t="shared" si="3"/>
-        <v>2760</v>
-      </c>
-      <c r="F6" s="14"/>
-      <c r="H6">
+      <c r="B6" s="21">
+        <f t="shared" si="0"/>
+        <v>2760</v>
+      </c>
+      <c r="C6" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D6" s="21">
+        <f>SUMIFS($L$2:$L$7,$K$2:$K$7,"&gt;="&amp;$A6,$K$2:$K$7,"&lt;"&amp;EDATE($A6,1))</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="21">
+        <f t="shared" si="2"/>
+        <v>2760</v>
+      </c>
+      <c r="F6" s="24"/>
+      <c r="G6" s="26">
+        <f>SUM(E2:E6)</f>
+        <v>13800</v>
+      </c>
+      <c r="I6" s="25"/>
+      <c r="J6">
         <v>2027</v>
       </c>
-      <c r="I6" s="10">
+      <c r="K6" s="10">
         <v>46784</v>
       </c>
-      <c r="J6" s="11">
+      <c r="L6" s="11">
         <f>(IF(2027=2026,Base_Annual_Salary_2026,IF(2027=2027,Base_Annual_Salary_2026*(1+Appraisal_Raise_Pct_Jan2027*Appraisal_Proration_Jan2027),(Base_Annual_Salary_2026*(1+Appraisal_Raise_Pct_Jan2027*Appraisal_Proration_Jan2027))*(1+Appraisal_Raise_Pct_Jan2028))))*LPTA_Annual_Grant_Pct*1/4</f>
-        <v>1278.2249999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="18">
         <f>EDATE($A$2,5)</f>
         <v>46388</v>
       </c>
-      <c r="B7" s="9">
-        <f t="shared" si="0"/>
-        <v>2840.5</v>
-      </c>
-      <c r="C7" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D7" s="9">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E7" s="9">
-        <f t="shared" si="3"/>
-        <v>2840.5</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7">
+      <c r="B7" s="19">
+        <f t="shared" si="0"/>
+        <v>2760</v>
+      </c>
+      <c r="C7" s="19">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D7" s="19">
+        <f>SUMIFS($L$2:$L$7,$K$2:$K$7,"&gt;="&amp;$A7,$K$2:$K$7,"&lt;"&amp;EDATE($A7,1))</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="19">
+        <f t="shared" si="2"/>
+        <v>2760</v>
+      </c>
+      <c r="I7" s="25"/>
+      <c r="J7">
         <v>2027</v>
       </c>
-      <c r="I7" s="10">
+      <c r="K7" s="10">
         <v>46966</v>
       </c>
-      <c r="J7" s="11">
+      <c r="L7" s="11">
         <f>(IF(2027=2026,Base_Annual_Salary_2026,IF(2027=2027,Base_Annual_Salary_2026*(1+Appraisal_Raise_Pct_Jan2027*Appraisal_Proration_Jan2027),(Base_Annual_Salary_2026*(1+Appraisal_Raise_Pct_Jan2027*Appraisal_Proration_Jan2027))*(1+Appraisal_Raise_Pct_Jan2028))))*LPTA_Annual_Grant_Pct*1/4</f>
-        <v>1278.2249999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <f>EDATE($A$2,6)</f>
         <v>46419</v>
       </c>
       <c r="B8" s="9">
         <f t="shared" si="0"/>
-        <v>2840.5</v>
+        <v>2760</v>
       </c>
       <c r="C8" s="9">
         <f t="shared" si="1"/>
-        <v>966.00000000000011</v>
+        <v>0</v>
       </c>
       <c r="D8" s="9">
-        <f t="shared" si="2"/>
-        <v>517.5</v>
+        <f>SUMIFS($L$2:$L$7,$K$2:$K$7,"&gt;="&amp;$A8,$K$2:$K$7,"&lt;"&amp;EDATE($A8,1))</f>
+        <v>0</v>
       </c>
       <c r="E8" s="9">
-        <f t="shared" si="3"/>
-        <v>4324</v>
-      </c>
-      <c r="F8" s="13">
-        <f>SUM(E7:E18)</f>
-        <v>37280.01</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+        <f t="shared" si="2"/>
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <f>EDATE($A$2,7)</f>
         <v>46447</v>
       </c>
       <c r="B9" s="9">
         <f t="shared" si="0"/>
-        <v>2840.5</v>
+        <v>2760</v>
       </c>
       <c r="C9" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D9" s="9">
-        <f t="shared" si="2"/>
+        <f>SUMIFS($L$2:$L$7,$K$2:$K$7,"&gt;="&amp;$A9,$K$2:$K$7,"&lt;"&amp;EDATE($A9,1))</f>
         <v>0</v>
       </c>
       <c r="E9" s="9">
-        <f t="shared" si="3"/>
-        <v>2840.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+        <f t="shared" si="2"/>
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <f>EDATE($A$2,8)</f>
         <v>46478</v>
       </c>
       <c r="B10" s="9">
         <f t="shared" si="0"/>
-        <v>2840.5</v>
+        <v>2760</v>
       </c>
       <c r="C10" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D10" s="9">
-        <f t="shared" si="2"/>
+        <f>SUMIFS($L$2:$L$7,$K$2:$K$7,"&gt;="&amp;$A10,$K$2:$K$7,"&lt;"&amp;EDATE($A10,1))</f>
         <v>0</v>
       </c>
       <c r="E10" s="9">
-        <f t="shared" si="3"/>
-        <v>2840.5</v>
-      </c>
-      <c r="F10" s="14"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+        <f t="shared" si="2"/>
+        <v>2760</v>
+      </c>
+      <c r="F10" s="13"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <f>EDATE($A$2,9)</f>
         <v>46508</v>
       </c>
       <c r="B11" s="9">
         <f t="shared" si="0"/>
-        <v>2840.5</v>
+        <v>2760</v>
       </c>
       <c r="C11" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D11" s="9">
-        <f t="shared" si="2"/>
+        <f>SUMIFS($L$2:$L$7,$K$2:$K$7,"&gt;="&amp;$A11,$K$2:$K$7,"&lt;"&amp;EDATE($A11,1))</f>
         <v>0</v>
       </c>
       <c r="E11" s="9">
-        <f t="shared" si="3"/>
-        <v>2840.5</v>
-      </c>
-      <c r="F11" s="14"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+        <f t="shared" si="2"/>
+        <v>2760</v>
+      </c>
+      <c r="F11" s="13"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <f>EDATE($A$2,10)</f>
         <v>46539</v>
       </c>
       <c r="B12" s="9">
         <f t="shared" si="0"/>
-        <v>2840.5</v>
+        <v>2760</v>
       </c>
       <c r="C12" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D12" s="9">
-        <f t="shared" si="2"/>
+        <f>SUMIFS($L$2:$L$7,$K$2:$K$7,"&gt;="&amp;$A12,$K$2:$K$7,"&lt;"&amp;EDATE($A12,1))</f>
         <v>0</v>
       </c>
       <c r="E12" s="9">
-        <f t="shared" si="3"/>
-        <v>2840.5</v>
-      </c>
-      <c r="F12" s="14"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+        <f t="shared" si="2"/>
+        <v>2760</v>
+      </c>
+      <c r="F12" s="13"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <f>EDATE($A$2,11)</f>
         <v>46569</v>
       </c>
       <c r="B13" s="9">
         <f t="shared" si="0"/>
-        <v>2840.5</v>
+        <v>2760</v>
       </c>
       <c r="C13" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D13" s="9">
-        <f t="shared" si="2"/>
+        <f>SUMIFS($L$2:$L$7,$K$2:$K$7,"&gt;="&amp;$A13,$K$2:$K$7,"&lt;"&amp;EDATE($A13,1))</f>
         <v>0</v>
       </c>
       <c r="E13" s="9">
-        <f t="shared" si="3"/>
-        <v>2840.5</v>
-      </c>
-      <c r="F13" s="14"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+        <f t="shared" si="2"/>
+        <v>2760</v>
+      </c>
+      <c r="F13" s="13"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <f>EDATE($A$2,12)</f>
         <v>46600</v>
       </c>
       <c r="B14" s="9">
         <f t="shared" si="0"/>
-        <v>2840.5</v>
+        <v>2760</v>
       </c>
       <c r="C14" s="9">
         <f t="shared" si="1"/>
-        <v>1193.0100000000002</v>
+        <v>0</v>
       </c>
       <c r="D14" s="9">
-        <f t="shared" si="2"/>
-        <v>517.5</v>
+        <f>SUMIFS($L$2:$L$7,$K$2:$K$7,"&gt;="&amp;$A14,$K$2:$K$7,"&lt;"&amp;EDATE($A14,1))</f>
+        <v>0</v>
       </c>
       <c r="E14" s="9">
-        <f t="shared" si="3"/>
-        <v>4551.01</v>
-      </c>
-      <c r="F14" s="14"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+        <f t="shared" si="2"/>
+        <v>2760</v>
+      </c>
+      <c r="F14" s="13"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <f>EDATE($A$2,13)</f>
         <v>46631</v>
       </c>
       <c r="B15" s="9">
         <f t="shared" si="0"/>
-        <v>2840.5</v>
+        <v>2760</v>
       </c>
       <c r="C15" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D15" s="9">
-        <f t="shared" si="2"/>
+        <f>SUMIFS($L$2:$L$7,$K$2:$K$7,"&gt;="&amp;$A15,$K$2:$K$7,"&lt;"&amp;EDATE($A15,1))</f>
         <v>0</v>
       </c>
       <c r="E15" s="9">
-        <f t="shared" si="3"/>
-        <v>2840.5</v>
-      </c>
-      <c r="F15" s="14"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+        <f t="shared" si="2"/>
+        <v>2760</v>
+      </c>
+      <c r="F15" s="13"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <f>EDATE($A$2,14)</f>
         <v>46661</v>
       </c>
       <c r="B16" s="9">
         <f t="shared" si="0"/>
-        <v>2840.5</v>
+        <v>2760</v>
       </c>
       <c r="C16" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D16" s="9">
-        <f t="shared" si="2"/>
+        <f>SUMIFS($L$2:$L$7,$K$2:$K$7,"&gt;="&amp;$A16,$K$2:$K$7,"&lt;"&amp;EDATE($A16,1))</f>
         <v>0</v>
       </c>
       <c r="E16" s="9">
-        <f t="shared" si="3"/>
-        <v>2840.5</v>
-      </c>
-      <c r="F16" s="14"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+        <f t="shared" si="2"/>
+        <v>2760</v>
+      </c>
+      <c r="F16" s="13"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <f>EDATE($A$2,15)</f>
         <v>46692</v>
       </c>
       <c r="B17" s="9">
         <f t="shared" si="0"/>
-        <v>2840.5</v>
+        <v>2760</v>
       </c>
       <c r="C17" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D17" s="9">
-        <f t="shared" si="2"/>
+        <f>SUMIFS($L$2:$L$7,$K$2:$K$7,"&gt;="&amp;$A17,$K$2:$K$7,"&lt;"&amp;EDATE($A17,1))</f>
         <v>0</v>
       </c>
       <c r="E17" s="9">
-        <f t="shared" si="3"/>
-        <v>2840.5</v>
-      </c>
-      <c r="F17" s="14"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="8">
+        <f t="shared" si="2"/>
+        <v>2760</v>
+      </c>
+      <c r="F17" s="13"/>
+      <c r="G17" s="23" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="20">
         <f>EDATE($A$2,16)</f>
         <v>46722</v>
       </c>
-      <c r="B18" s="9">
-        <f t="shared" si="0"/>
-        <v>2840.5</v>
-      </c>
-      <c r="C18" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D18" s="9">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E18" s="9">
-        <f t="shared" si="3"/>
-        <v>2840.5</v>
-      </c>
-      <c r="F18" s="14"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="8">
+      <c r="B18" s="21">
+        <f t="shared" si="0"/>
+        <v>2760</v>
+      </c>
+      <c r="C18" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D18" s="21">
+        <f>SUMIFS($L$2:$L$7,$K$2:$K$7,"&gt;="&amp;$A18,$K$2:$K$7,"&lt;"&amp;EDATE($A18,1))</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="21">
+        <f t="shared" si="2"/>
+        <v>2760</v>
+      </c>
+      <c r="F18" s="24"/>
+      <c r="G18" s="26">
+        <f>SUM(E7:E18)</f>
+        <v>33120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="18">
         <f>EDATE($A$2,17)</f>
         <v>46753</v>
       </c>
-      <c r="B19" s="9">
-        <f t="shared" si="0"/>
-        <v>3039.3350000000005</v>
-      </c>
-      <c r="C19" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D19" s="9">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E19" s="9">
-        <f t="shared" si="3"/>
-        <v>3039.3350000000005</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B19" s="19">
+        <f t="shared" si="0"/>
+        <v>2760</v>
+      </c>
+      <c r="C19" s="19">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D19" s="19">
+        <f>SUMIFS($L$2:$L$7,$K$2:$K$7,"&gt;="&amp;$A19,$K$2:$K$7,"&lt;"&amp;EDATE($A19,1))</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="19">
+        <f t="shared" si="2"/>
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <f>EDATE($A$2,18)</f>
         <v>46784</v>
       </c>
       <c r="B20" s="9">
         <f t="shared" si="0"/>
-        <v>3039.3350000000005</v>
+        <v>2760</v>
       </c>
       <c r="C20" s="9">
         <f t="shared" si="1"/>
-        <v>1193.0100000000002</v>
+        <v>0</v>
       </c>
       <c r="D20" s="9">
-        <f t="shared" si="2"/>
-        <v>1795.7249999999999</v>
+        <f>SUMIFS($L$2:$L$7,$K$2:$K$7,"&gt;="&amp;$A20,$K$2:$K$7,"&lt;"&amp;EDATE($A20,1))</f>
+        <v>0</v>
       </c>
       <c r="E20" s="9">
-        <f t="shared" si="3"/>
-        <v>6028.0700000000015</v>
-      </c>
-      <c r="F20" s="13">
-        <f>SUM(E19:E30)</f>
-        <v>42533.000699999997</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+        <f t="shared" si="2"/>
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <f>EDATE($A$2,19)</f>
         <v>46813</v>
       </c>
       <c r="B21" s="9">
         <f t="shared" si="0"/>
-        <v>3039.3350000000005</v>
+        <v>2760</v>
       </c>
       <c r="C21" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D21" s="9">
-        <f t="shared" si="2"/>
+        <f>SUMIFS($L$2:$L$7,$K$2:$K$7,"&gt;="&amp;$A21,$K$2:$K$7,"&lt;"&amp;EDATE($A21,1))</f>
         <v>0</v>
       </c>
       <c r="E21" s="9">
-        <f t="shared" si="3"/>
-        <v>3039.3350000000005</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+        <f t="shared" si="2"/>
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <f>EDATE($A$2,20)</f>
         <v>46844</v>
       </c>
       <c r="B22" s="9">
         <f t="shared" si="0"/>
-        <v>3039.3350000000005</v>
+        <v>2760</v>
       </c>
       <c r="C22" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D22" s="9">
-        <f t="shared" si="2"/>
+        <f>SUMIFS($L$2:$L$7,$K$2:$K$7,"&gt;="&amp;$A22,$K$2:$K$7,"&lt;"&amp;EDATE($A22,1))</f>
         <v>0</v>
       </c>
       <c r="E22" s="9">
-        <f t="shared" si="3"/>
-        <v>3039.3350000000005</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+        <f t="shared" si="2"/>
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <f>EDATE($A$2,21)</f>
         <v>46874</v>
       </c>
       <c r="B23" s="9">
         <f t="shared" si="0"/>
-        <v>3039.3350000000005</v>
+        <v>2760</v>
       </c>
       <c r="C23" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D23" s="9">
-        <f t="shared" si="2"/>
+        <f>SUMIFS($L$2:$L$7,$K$2:$K$7,"&gt;="&amp;$A23,$K$2:$K$7,"&lt;"&amp;EDATE($A23,1))</f>
         <v>0</v>
       </c>
       <c r="E23" s="9">
-        <f t="shared" si="3"/>
-        <v>3039.3350000000005</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+        <f t="shared" si="2"/>
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <f>EDATE($A$2,22)</f>
         <v>46905</v>
       </c>
       <c r="B24" s="9">
         <f t="shared" si="0"/>
-        <v>3039.3350000000005</v>
+        <v>2760</v>
       </c>
       <c r="C24" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D24" s="9">
-        <f t="shared" si="2"/>
+        <f>SUMIFS($L$2:$L$7,$K$2:$K$7,"&gt;="&amp;$A24,$K$2:$K$7,"&lt;"&amp;EDATE($A24,1))</f>
         <v>0</v>
       </c>
       <c r="E24" s="9">
-        <f t="shared" si="3"/>
-        <v>3039.3350000000005</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+        <f t="shared" si="2"/>
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <f>EDATE($A$2,23)</f>
         <v>46935</v>
       </c>
       <c r="B25" s="9">
         <f t="shared" si="0"/>
-        <v>3039.3350000000005</v>
+        <v>2760</v>
       </c>
       <c r="C25" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D25" s="9">
-        <f t="shared" si="2"/>
+        <f>SUMIFS($L$2:$L$7,$K$2:$K$7,"&gt;="&amp;$A25,$K$2:$K$7,"&lt;"&amp;EDATE($A25,1))</f>
         <v>0</v>
       </c>
       <c r="E25" s="9">
-        <f t="shared" si="3"/>
-        <v>3039.3350000000005</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+        <f t="shared" si="2"/>
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <f>EDATE($A$2,24)</f>
         <v>46966</v>
       </c>
       <c r="B26" s="9">
         <f t="shared" si="0"/>
-        <v>3039.3350000000005</v>
+        <v>2760</v>
       </c>
       <c r="C26" s="9">
         <f t="shared" si="1"/>
-        <v>1276.5207000000003</v>
+        <v>0</v>
       </c>
       <c r="D26" s="9">
-        <f t="shared" si="2"/>
-        <v>1795.7249999999999</v>
+        <f>SUMIFS($L$2:$L$7,$K$2:$K$7,"&gt;="&amp;$A26,$K$2:$K$7,"&lt;"&amp;EDATE($A26,1))</f>
+        <v>0</v>
       </c>
       <c r="E26" s="9">
-        <f t="shared" si="3"/>
-        <v>6111.5807000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+        <f t="shared" si="2"/>
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <f>EDATE($A$2,25)</f>
         <v>46997</v>
       </c>
       <c r="B27" s="9">
         <f t="shared" si="0"/>
-        <v>3039.3350000000005</v>
+        <v>2760</v>
       </c>
       <c r="C27" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D27" s="9">
-        <f t="shared" si="2"/>
+        <f>SUMIFS($L$2:$L$7,$K$2:$K$7,"&gt;="&amp;$A27,$K$2:$K$7,"&lt;"&amp;EDATE($A27,1))</f>
         <v>0</v>
       </c>
       <c r="E27" s="9">
-        <f t="shared" si="3"/>
-        <v>3039.3350000000005</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+        <f t="shared" si="2"/>
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <f>EDATE($A$2,26)</f>
         <v>47027</v>
       </c>
       <c r="B28" s="9">
         <f t="shared" si="0"/>
-        <v>3039.3350000000005</v>
+        <v>2760</v>
       </c>
       <c r="C28" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D28" s="9">
-        <f t="shared" si="2"/>
+        <f>SUMIFS($L$2:$L$7,$K$2:$K$7,"&gt;="&amp;$A28,$K$2:$K$7,"&lt;"&amp;EDATE($A28,1))</f>
         <v>0</v>
       </c>
       <c r="E28" s="9">
-        <f t="shared" si="3"/>
-        <v>3039.3350000000005</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+        <f t="shared" si="2"/>
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
         <f>EDATE($A$2,27)</f>
         <v>47058</v>
       </c>
       <c r="B29" s="9">
         <f t="shared" si="0"/>
-        <v>3039.3350000000005</v>
+        <v>2760</v>
       </c>
       <c r="C29" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D29" s="9">
-        <f t="shared" si="2"/>
+        <f>SUMIFS($L$2:$L$7,$K$2:$K$7,"&gt;="&amp;$A29,$K$2:$K$7,"&lt;"&amp;EDATE($A29,1))</f>
         <v>0</v>
       </c>
       <c r="E29" s="9">
-        <f t="shared" si="3"/>
-        <v>3039.3350000000005</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="8">
+        <f t="shared" si="2"/>
+        <v>2760</v>
+      </c>
+      <c r="G29" s="23" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="20">
         <f>EDATE($A$2,28)</f>
         <v>47088</v>
       </c>
-      <c r="B30" s="9">
-        <f t="shared" si="0"/>
-        <v>3039.3350000000005</v>
-      </c>
-      <c r="C30" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D30" s="9">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E30" s="9">
-        <f t="shared" si="3"/>
-        <v>3039.3350000000005</v>
-      </c>
-    </row>
+      <c r="B30" s="21">
+        <f t="shared" si="0"/>
+        <v>2760</v>
+      </c>
+      <c r="C30" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D30" s="21">
+        <f>SUMIFS($L$2:$L$7,$K$2:$K$7,"&gt;="&amp;$A30,$K$2:$K$7,"&lt;"&amp;EDATE($A30,1))</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="21">
+        <f t="shared" si="2"/>
+        <v>2760</v>
+      </c>
+      <c r="F30" s="22"/>
+      <c r="G30" s="26">
+        <f>SUM(E19:E30)</f>
+        <v>33120</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
